--- a/479-préparation-publication-release-240-ballot/ig/ValueSet-tddui-cim-10.xlsx
+++ b/479-préparation-publication-release-240-ballot/ig/ValueSet-tddui-cim-10.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T09:02:12+00:00</t>
+    <t>2026-06-15T09:19:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
